--- a/data/Web3 wallets.xlsx
+++ b/data/Web3 wallets.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="57490" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="24" activeTab="29" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="investment" sheetId="1" state="visible" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="bitget" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="bybit" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="photon" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ledger1" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -46,7 +47,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +69,11 @@
       <color theme="4" tint="-0.249977111117893"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -103,12 +109,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -151,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +187,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -703,62 +727,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -784,16 +808,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4230.089352637437</v>
+        <v>3411.13512298008</v>
       </c>
       <c r="I2" t="n">
-        <v>884.1309755947507</v>
+        <v>712.9613520540665</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>884.1309755947507</v>
+        <v>712.9613520540665</v>
       </c>
     </row>
     <row r="3">
@@ -816,16 +840,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>0.764159</v>
       </c>
       <c r="I3" t="n">
-        <v>165.368</v>
+        <v>90.26246108000001</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>165.368</v>
+        <v>90.26246108000001</v>
       </c>
     </row>
   </sheetData>
@@ -843,62 +867,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -929,16 +953,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4230.089352637437</v>
+        <v>3411.13512298008</v>
       </c>
       <c r="I2" t="n">
-        <v>14.80531273423103</v>
+        <v>11.93897293043028</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>14.80531273423103</v>
+        <v>11.93897293043028</v>
       </c>
     </row>
     <row r="3">
@@ -966,16 +990,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4230.089352637437</v>
+        <v>3411.13512298008</v>
       </c>
       <c r="I3" t="n">
-        <v>4.230089352637437</v>
+        <v>3.41113512298008</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.230089352637437</v>
+        <v>3.41113512298008</v>
       </c>
     </row>
     <row r="4">
@@ -1003,16 +1027,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4230.089352637437</v>
+        <v>3411.13512298008</v>
       </c>
       <c r="I4" t="n">
-        <v>16.92035741054975</v>
+        <v>13.64454049192032</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16.92035741054975</v>
+        <v>13.64454049192032</v>
       </c>
     </row>
     <row r="5">
@@ -1035,16 +1059,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4230.089352637437</v>
+        <v>3411.13512298008</v>
       </c>
       <c r="I5" t="n">
-        <v>62.66454366997099</v>
+        <v>50.5325557118269</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>62.66454366997099</v>
+        <v>50.5325557118269</v>
       </c>
     </row>
     <row r="6">
@@ -1067,16 +1091,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996392491767921</v>
       </c>
       <c r="I6" t="n">
-        <v>213.2792959879744</v>
+        <v>213.2230518494098</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>213.2792959879744</v>
+        <v>213.2230518494098</v>
       </c>
     </row>
     <row r="7">
@@ -1099,16 +1123,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.21</v>
+        <v>0.8310650000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>88.33</v>
+        <v>60.667745</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>88.33</v>
+        <v>60.667745</v>
       </c>
     </row>
   </sheetData>
@@ -1126,62 +1150,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1199,7 +1223,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1207,16 +1231,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>206.0547832424675</v>
+        <v>154.2665544569048</v>
       </c>
       <c r="I2" t="n">
-        <v>115.3906786157818</v>
+        <v>84.84660495129765</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>115.3906786157818</v>
+        <v>84.84660495129765</v>
       </c>
     </row>
     <row r="3">
@@ -1231,7 +1255,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1239,16 +1263,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996392491767921</v>
       </c>
       <c r="I3" t="n">
-        <v>293.9714628244935</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>293.9714628244935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1263,7 +1287,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>2112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1271,16 +1295,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996392491767921</v>
       </c>
       <c r="I4" t="n">
-        <v>999.9029347771889</v>
+        <v>2111.238094261385</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>999.9029347771889</v>
+        <v>2111.238094261385</v>
       </c>
     </row>
     <row r="5">
@@ -1295,7 +1319,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1303,16 +1327,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>206.0547832424675</v>
+        <v>154.2665544569048</v>
       </c>
       <c r="I5" t="n">
-        <v>618.1643497274026</v>
+        <v>465.8849944598525</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>618.1643497274026</v>
+        <v>465.8849944598525</v>
       </c>
     </row>
   </sheetData>
@@ -1330,62 +1354,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1411,16 +1435,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000892016020366</v>
+        <v>0.9995250237622161</v>
       </c>
       <c r="I2" t="n">
-        <v>145.1293423229531</v>
+        <v>144.9311284455213</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>145.1293423229531</v>
+        <v>144.9311284455213</v>
       </c>
     </row>
     <row r="3">
@@ -1443,16 +1467,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="I3" t="n">
-        <v>4.963358755614392</v>
+        <v>3.410286813221191</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.963358755614392</v>
+        <v>3.410286813221191</v>
       </c>
     </row>
     <row r="4">
@@ -1480,16 +1504,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999765316198375</v>
+        <v>0.9996392491767921</v>
       </c>
       <c r="I4" t="n">
-        <v>97.99770009874408</v>
+        <v>97.96464641932563</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>97.99770009874408</v>
+        <v>97.96464641932563</v>
       </c>
     </row>
     <row r="5">
@@ -1512,16 +1536,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>206.0874120898517</v>
+        <v>154.2665544569048</v>
       </c>
       <c r="I5" t="n">
-        <v>25.1426642749619</v>
+        <v>18.82051964374239</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>25.1426642749619</v>
+        <v>18.82051964374239</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1568,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="I6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
     </row>
     <row r="7">
@@ -1576,16 +1600,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>115230.0028671602</v>
+        <v>103037.3785919885</v>
       </c>
       <c r="I7" t="n">
-        <v>8.066100200701216</v>
+        <v>7.212616501439194</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8.066100200701216</v>
+        <v>7.212616501439194</v>
       </c>
     </row>
     <row r="8">
@@ -1608,16 +1632,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3927566527327648</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I8" t="n">
-        <v>8.48354369902772</v>
+        <v>7.225084484130478</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8.48354369902772</v>
+        <v>7.225084484130478</v>
       </c>
     </row>
   </sheetData>
@@ -1635,62 +1659,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1716,16 +1740,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000297458170462</v>
       </c>
       <c r="I2" t="n">
-        <v>115.9972776679011</v>
+        <v>116.0345051477735</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>115.9972776679011</v>
+        <v>116.0345051477735</v>
       </c>
     </row>
     <row r="3">
@@ -1748,16 +1772,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="I3" t="n">
-        <v>7.182272081653768</v>
+        <v>4.934885623837722</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7.182272081653768</v>
+        <v>4.934885623837722</v>
       </c>
     </row>
     <row r="4">
@@ -1785,16 +1809,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000297458170462</v>
       </c>
       <c r="I4" t="n">
-        <v>102.3975968378714</v>
+        <v>102.4304597166553</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>102.3975968378714</v>
+        <v>102.4304597166553</v>
       </c>
     </row>
     <row r="5">
@@ -1817,16 +1841,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>206.0874120898517</v>
+        <v>154.3872130630848</v>
       </c>
       <c r="I5" t="n">
-        <v>33.28311705251105</v>
+        <v>24.9335349096882</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>33.28311705251105</v>
+        <v>24.9335349096882</v>
       </c>
     </row>
     <row r="6">
@@ -1849,16 +1873,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="I6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.919622797420231</v>
+        <v>2.0060510666007</v>
       </c>
     </row>
     <row r="7">
@@ -1881,16 +1905,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.000892016020366</v>
+        <v>0.9995250237622161</v>
       </c>
       <c r="I7" t="n">
-        <v>7.006244112142564</v>
+        <v>6.996675166335512</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7.006244112142564</v>
+        <v>6.996675166335512</v>
       </c>
     </row>
     <row r="8">
@@ -1913,16 +1937,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3927566527327648</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I8" t="n">
-        <v>8.522819364300995</v>
+        <v>7.258533949334785</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8.522819364300995</v>
+        <v>7.258533949334785</v>
       </c>
     </row>
   </sheetData>
@@ -1940,62 +1964,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2021,16 +2045,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000892016020366</v>
+        <v>0.9995250237622161</v>
       </c>
       <c r="I2" t="n">
-        <v>106.64504430697</v>
+        <v>106.4993912818641</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>106.64504430697</v>
+        <v>106.4993912818641</v>
       </c>
     </row>
     <row r="3">
@@ -2053,16 +2077,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0874120898517</v>
+        <v>154.3872130630848</v>
       </c>
       <c r="I3" t="n">
-        <v>43.66992262183957</v>
+        <v>32.71465044806767</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>43.66992262183957</v>
+        <v>32.71465044806767</v>
       </c>
     </row>
     <row r="4">
@@ -2085,16 +2109,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3927566527327648</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I4" t="n">
-        <v>8.589587995265566</v>
+        <v>7.315398040182108</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8.589587995265566</v>
+        <v>7.315398040182108</v>
       </c>
     </row>
   </sheetData>
@@ -2112,62 +2136,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2193,16 +2217,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000892016020366</v>
+        <v>0.9995250237622161</v>
       </c>
       <c r="I2" t="n">
-        <v>113.0007086086994</v>
+        <v>112.8463751827542</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>113.0007086086994</v>
+        <v>112.8463751827542</v>
       </c>
     </row>
     <row r="3">
@@ -2225,16 +2249,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0874120898517</v>
+        <v>154.3872130630848</v>
       </c>
       <c r="I3" t="n">
-        <v>19.04247687710229</v>
+        <v>14.26537848702904</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>19.04247687710229</v>
+        <v>14.26537848702904</v>
       </c>
     </row>
     <row r="4">
@@ -2257,16 +2281,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3927566527327648</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I4" t="n">
-        <v>8.723125257194706</v>
+        <v>7.429126221876755</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8.723125257194706</v>
+        <v>7.429126221876755</v>
       </c>
     </row>
   </sheetData>
@@ -2284,62 +2308,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2370,7 +2394,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2402,16 +2426,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>11.68667061666399</v>
+        <v>8.028172505132877</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11.68667061666399</v>
+        <v>8.028172505132877</v>
       </c>
     </row>
     <row r="4">
@@ -2434,16 +2458,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -2466,16 +2490,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I5" t="n">
-        <v>43.82501481248998</v>
+        <v>30.10564689424829</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>43.82501481248998</v>
+        <v>30.10564689424829</v>
       </c>
     </row>
     <row r="6">
@@ -2498,16 +2522,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I6" t="n">
-        <v>119.9971837943805</v>
+        <v>120.001297792294</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>119.9971837943805</v>
+        <v>120.001297792294</v>
       </c>
     </row>
   </sheetData>
@@ -2525,62 +2549,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2611,16 +2635,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
-        <v>9.749771183293415</v>
+        <v>9.750105445623884</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9.749771183293415</v>
+        <v>9.750105445623884</v>
       </c>
     </row>
     <row r="3">
@@ -2643,16 +2667,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>20.45167357916199</v>
+        <v>14.04930188398253</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>20.45167357916199</v>
+        <v>14.04930188398253</v>
       </c>
     </row>
     <row r="4">
@@ -2675,16 +2699,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -2707,16 +2731,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I5" t="n">
-        <v>73.04169135414996</v>
+        <v>50.17607815708048</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>73.04169135414996</v>
+        <v>50.17607815708048</v>
       </c>
     </row>
   </sheetData>
@@ -2734,62 +2758,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2820,16 +2844,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
-        <v>4.829886647723815</v>
+        <v>4.830052236139831</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4.829886647723815</v>
+        <v>4.830052236139831</v>
       </c>
     </row>
     <row r="3">
@@ -2852,16 +2876,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>7.012002369998396</v>
+        <v>4.816903503079726</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7.012002369998396</v>
+        <v>4.816903503079726</v>
       </c>
     </row>
     <row r="4">
@@ -2884,16 +2908,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -2916,16 +2940,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I5" t="n">
-        <v>20.45167357916199</v>
+        <v>14.04930188398253</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20.45167357916199</v>
+        <v>14.04930188398253</v>
       </c>
     </row>
   </sheetData>
@@ -2956,62 +2980,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3042,7 +3066,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3074,16 +3098,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>5.259001777498797</v>
+        <v>3.612677627309795</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5.259001777498797</v>
+        <v>3.612677627309795</v>
       </c>
     </row>
     <row r="4">
@@ -3106,16 +3130,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -3138,16 +3162,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I5" t="n">
-        <v>6.427668839165197</v>
+        <v>4.415494877823083</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6.427668839165197</v>
+        <v>4.415494877823083</v>
       </c>
     </row>
   </sheetData>
@@ -3165,62 +3189,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3251,7 +3275,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3283,16 +3307,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>4.966835012082197</v>
+        <v>3.411973314681473</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.966835012082197</v>
+        <v>3.411973314681473</v>
       </c>
     </row>
     <row r="4">
@@ -3315,16 +3339,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -3347,16 +3371,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>115233.4918673834</v>
+        <v>103017.3211094058</v>
       </c>
       <c r="I5" t="n">
-        <v>11.52334918673834</v>
+        <v>10.30173211094058</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11.52334918673834</v>
+        <v>10.30173211094058</v>
       </c>
     </row>
   </sheetData>
@@ -3374,62 +3398,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3460,7 +3484,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765316198375</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3492,16 +3516,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I3" t="n">
-        <v>5.843335308331997</v>
+        <v>4.014086252566439</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5.843335308331997</v>
+        <v>4.014086252566439</v>
       </c>
     </row>
     <row r="4">
@@ -3524,16 +3548,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
     </row>
     <row r="5">
@@ -3556,16 +3580,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.921667654165998</v>
+        <v>2.007043126283219</v>
       </c>
       <c r="I5" t="n">
-        <v>11.68667061666399</v>
+        <v>8.028172505132877</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11.68667061666399</v>
+        <v>8.028172505132877</v>
       </c>
     </row>
   </sheetData>
@@ -3583,62 +3607,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3669,16 +3693,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>1.000010814935783</v>
       </c>
       <c r="I2" t="n">
-        <v>18.11957460621821</v>
+        <v>18.12019596663639</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>18.11957460621821</v>
+        <v>18.12019596663639</v>
       </c>
     </row>
     <row r="3">
@@ -3701,16 +3725,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>5.848984279809498</v>
+        <v>4.016085014170712</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5.848984279809498</v>
+        <v>4.016085014170712</v>
       </c>
     </row>
     <row r="4">
@@ -3733,16 +3757,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
     </row>
     <row r="5">
@@ -3765,16 +3789,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.001003728019676</v>
+        <v>0.9996298292303516</v>
       </c>
       <c r="I5" t="n">
-        <v>50.05018640098379</v>
+        <v>49.98149146151758</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>50.05018640098379</v>
+        <v>49.98149146151758</v>
       </c>
     </row>
   </sheetData>
@@ -3792,62 +3816,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3878,16 +3902,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I2" t="n">
-        <v>13.51968259801712</v>
+        <v>13.51778899074641</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>13.51968259801712</v>
+        <v>13.51778899074641</v>
       </c>
     </row>
     <row r="3">
@@ -3910,16 +3934,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>8.773476419714246</v>
+        <v>6.024127521256068</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8.773476419714246</v>
+        <v>6.024127521256068</v>
       </c>
     </row>
     <row r="4">
@@ -3942,16 +3966,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
     </row>
     <row r="5">
@@ -3974,16 +3998,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I5" t="n">
-        <v>58.48984279809498</v>
+        <v>40.16085014170712</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>58.48984279809498</v>
+        <v>40.16085014170712</v>
       </c>
     </row>
   </sheetData>
@@ -4001,62 +4025,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4087,16 +4111,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I2" t="n">
-        <v>9.19978401640218</v>
+        <v>9.198495467075956</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9.19978401640218</v>
+        <v>9.198495467075956</v>
       </c>
     </row>
     <row r="3">
@@ -4119,16 +4143,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>10.23572248966662</v>
+        <v>7.028148774798746</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.23572248966662</v>
+        <v>7.028148774798746</v>
       </c>
     </row>
     <row r="4">
@@ -4151,16 +4175,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
     </row>
     <row r="5">
@@ -4183,16 +4207,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I5" t="n">
-        <v>58.48984279809498</v>
+        <v>40.16085014170712</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>58.48984279809498</v>
+        <v>40.16085014170712</v>
       </c>
     </row>
     <row r="6">
@@ -4215,16 +4239,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.001003728019676</v>
+        <v>0.9996298292303516</v>
       </c>
       <c r="I6" t="n">
-        <v>75.07527960147569</v>
+        <v>74.97223719227637</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>75.07527960147569</v>
+        <v>74.97223719227637</v>
       </c>
     </row>
   </sheetData>
@@ -4242,62 +4266,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4328,16 +4352,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I2" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
     </row>
     <row r="3">
@@ -4360,16 +4384,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>12.28286698759995</v>
+        <v>8.433778529758495</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12.28286698759995</v>
+        <v>8.433778529758495</v>
       </c>
     </row>
     <row r="4">
@@ -4392,16 +4416,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
     </row>
     <row r="5">
@@ -4424,16 +4448,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I5" t="n">
-        <v>52.64085851828548</v>
+        <v>36.14476512753641</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.64085851828548</v>
+        <v>36.14476512753641</v>
       </c>
     </row>
   </sheetData>
@@ -4451,62 +4475,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4537,16 +4561,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I2" t="n">
-        <v>68.99838012301636</v>
+        <v>68.98871600306967</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>68.99838012301636</v>
+        <v>68.98871600306967</v>
       </c>
     </row>
     <row r="3">
@@ -4569,16 +4593,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>3.509390567885699</v>
+        <v>2.409651008502427</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.509390567885699</v>
+        <v>2.409651008502427</v>
       </c>
     </row>
     <row r="4">
@@ -4601,16 +4625,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11697968559619</v>
+        <v>0.08032170028341425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.11697968559619</v>
+        <v>0.08032170028341425</v>
       </c>
     </row>
     <row r="5">
@@ -4633,16 +4657,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I5" t="n">
-        <v>3.509390567885699</v>
+        <v>2.409651008502427</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.509390567885699</v>
+        <v>2.409651008502427</v>
       </c>
     </row>
   </sheetData>
@@ -4660,62 +4684,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4746,16 +4770,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I2" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
     </row>
     <row r="3">
@@ -4778,16 +4802,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I3" t="n">
-        <v>9.358374847695197</v>
+        <v>6.425736022673139</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9.358374847695197</v>
+        <v>6.425736022673139</v>
       </c>
     </row>
     <row r="4">
@@ -4810,16 +4834,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.924492139904749</v>
+        <v>2.008042507085356</v>
       </c>
     </row>
     <row r="5">
@@ -4842,16 +4866,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9999765235219762</v>
+        <v>0.9998364638126039</v>
       </c>
       <c r="I5" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5.999859141131857</v>
+        <v>5.999018782875623</v>
       </c>
     </row>
   </sheetData>
@@ -4865,66 +4889,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4942,7 +4966,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1309</v>
+        <v>904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4950,16 +4974,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000819727842232</v>
+        <v>0.9996178844948936</v>
       </c>
       <c r="I2" t="n">
-        <v>1310.073023745481</v>
+        <v>903.6545675833838</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1310.073023745481</v>
+        <v>903.6545675833838</v>
       </c>
     </row>
     <row r="3">
@@ -4974,7 +4998,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2815</v>
+        <v>1887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4982,16 +5006,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.124234195437702</v>
+        <v>0.09969023884164674</v>
       </c>
       <c r="I3" t="n">
-        <v>349.7192601571312</v>
+        <v>188.1154806941874</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>349.7192601571312</v>
+        <v>188.1154806941874</v>
       </c>
     </row>
     <row r="4">
@@ -5006,7 +5030,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52.3</v>
+        <v>68.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5014,16 +5038,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.534527521506202</v>
+        <v>7.885030036835896</v>
       </c>
       <c r="I4" t="n">
-        <v>341.7557893747743</v>
+        <v>540.1245575232589</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>341.7557893747743</v>
+        <v>540.1245575232589</v>
       </c>
     </row>
     <row r="5">
@@ -5038,7 +5062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>547</v>
+        <v>1450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5046,16 +5070,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4612053263770833</v>
+        <v>0.3094321860691936</v>
       </c>
       <c r="I5" t="n">
-        <v>252.2793135282646</v>
+        <v>448.6766698003307</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>252.2793135282646</v>
+        <v>448.6766698003307</v>
       </c>
     </row>
     <row r="6">
@@ -5070,24 +5094,184 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9000</v>
+        <v>531.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2755701329957104</v>
+      </c>
+      <c r="I6" t="n">
+        <v>146.4379686739205</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>146.4379686739205</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SYRUP</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4351676593689429</v>
+      </c>
+      <c r="I7" t="n">
+        <v>102.6125340791967</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>102.6125340791967</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>864365</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TAG</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0005409107988505747</v>
+      </c>
+      <c r="I8" t="n">
+        <v>467.544362648477</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>467.544362648477</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.2987</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TAO</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>363.415260988639</v>
+      </c>
+      <c r="I9" t="n">
+        <v>471.9673994459455</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>471.9673994459455</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5.978548821095226</v>
+      </c>
+      <c r="I10" t="n">
+        <v>130.9302191819854</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>130.9302191819854</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>SWTCH</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0.111737</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1005.633</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1005.633</v>
+      <c r="H11" t="n">
+        <v>0.069079</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5654,62 +5838,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -5727,7 +5911,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>600</v>
+        <v>517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5735,16 +5919,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000819727842232</v>
+        <v>0.9996178844948936</v>
       </c>
       <c r="I2" t="n">
-        <v>600.491836705339</v>
+        <v>516.80244628386</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>600.491836705339</v>
+        <v>516.80244628386</v>
       </c>
     </row>
     <row r="3">
@@ -5767,16 +5951,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.616656826105162</v>
+        <v>2.391419593021868</v>
       </c>
       <c r="I3" t="n">
-        <v>172.6993505229407</v>
+        <v>157.8336931394433</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>172.6993505229407</v>
+        <v>157.8336931394433</v>
       </c>
     </row>
     <row r="4">
@@ -5799,7 +5983,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4612053263770833</v>
+        <v>0.3094321860691936</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5823,7 +6007,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1423</v>
+        <v>1520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5831,16 +6015,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.000819727842232</v>
+        <v>0.9996178844948936</v>
       </c>
       <c r="I5" t="n">
-        <v>1424.166472719496</v>
+        <v>1519.419184432238</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1424.166472719496</v>
+        <v>1519.419184432238</v>
       </c>
     </row>
     <row r="6">
@@ -5863,16 +6047,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.04092167</v>
+        <v>0.02803292</v>
       </c>
       <c r="I6" t="n">
-        <v>95.7567078</v>
+        <v>65.59703279999999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>95.7567078</v>
+        <v>65.59703279999999</v>
       </c>
     </row>
   </sheetData>
@@ -5890,62 +6074,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -5964,6 +6148,146 @@
       </c>
       <c r="C2" t="n">
         <v>0.0162</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>154.5759687869933</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.50413069434929</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.50413069434929</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CODEC</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01697825</v>
+      </c>
+      <c r="I3" t="n">
+        <v>203.739</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>203.739</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>rewards ticker</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>prices</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>rewards prices</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>rewards value</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>total value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5974,17 +6298,17 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>206.3378097645877</v>
+        <v>154.5759687869933</v>
       </c>
       <c r="I2" t="n">
-        <v>3.34267251818632</v>
+        <v>15.45759687869933</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.34267251818632</v>
+        <v>15.45759687869933</v>
       </c>
     </row>
     <row r="3">
@@ -5999,28 +6323,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12000</v>
+        <v>515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CODEC</t>
+          <t>USDC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.02104225</v>
+        <v>0.9998841125745066</v>
       </c>
       <c r="I3" t="n">
-        <v>252.507</v>
+        <v>514.9403179758709</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>252.507</v>
+        <v>514.9403179758709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>846</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.9996635053528707</v>
+      </c>
+      <c r="I4" t="n">
+        <v>845.7153255285286</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>845.7153255285286</v>
       </c>
     </row>
   </sheetData>
@@ -6155,66 +6515,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6240,16 +6600,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3923360528353861</v>
+        <v>0.3347222606834201</v>
       </c>
       <c r="I2" t="n">
-        <v>58.06573581963714</v>
+        <v>49.53889458114617</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>58.06573581963714</v>
+        <v>49.53889458114617</v>
       </c>
     </row>
     <row r="3">
@@ -6264,7 +6624,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6272,16 +6632,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I3" t="n">
-        <v>209.9796163032097</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>209.9796163032097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6296,7 +6656,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6309,16 +6669,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I4" t="n">
-        <v>166.9837901077905</v>
+        <v>168.9380244633936</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>166.9837901077905</v>
+        <v>168.9380244633936</v>
       </c>
     </row>
     <row r="5">
@@ -6333,7 +6693,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.314</v>
+        <v>0.1862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6341,16 +6701,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>206.0547832424675</v>
+        <v>154.3682946299502</v>
       </c>
       <c r="I5" t="n">
-        <v>64.7012019381348</v>
+        <v>28.74337646009672</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>64.7012019381348</v>
+        <v>28.74337646009672</v>
       </c>
     </row>
     <row r="6">
@@ -6365,7 +6725,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03356096</v>
+        <v>0.08089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6373,16 +6733,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4230.089352637437</v>
+        <v>3410.691845817456</v>
       </c>
       <c r="I6" t="n">
-        <v>141.9658595602909</v>
+        <v>275.8908634081741</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>141.9658595602909</v>
+        <v>275.8908634081741</v>
       </c>
     </row>
     <row r="7">
@@ -6397,7 +6757,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.00246</v>
+        <v>0.00662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6405,16 +6765,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>115230.0028671602</v>
+        <v>102898.9483825072</v>
       </c>
       <c r="I7" t="n">
-        <v>283.4658070532142</v>
+        <v>681.1910382921974</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>283.4658070532142</v>
+        <v>681.1910382921974</v>
       </c>
     </row>
     <row r="8">
@@ -6437,16 +6797,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.920754356690552</v>
+        <v>2.008710281543311</v>
       </c>
       <c r="I8" t="n">
-        <v>20.44528049683387</v>
+        <v>14.06097197080318</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20.44528049683387</v>
+        <v>14.06097197080318</v>
       </c>
     </row>
     <row r="9">
@@ -6461,7 +6821,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.99</v>
+        <v>27.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6469,16 +6829,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.920754356690552</v>
+        <v>2.008710281543311</v>
       </c>
       <c r="I9" t="n">
-        <v>2.891546813123647</v>
+        <v>55.03866171428672</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.891546813123647</v>
+        <v>55.03866171428672</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6853,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6501,16 +6861,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.920754356690552</v>
+        <v>2.008710281543311</v>
       </c>
       <c r="I10" t="n">
-        <v>87.62263070071657</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>87.62263070071657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6525,7 +6885,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30600</v>
+        <v>27684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6533,16 +6893,48 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.11216</v>
+        <v>0.068951</v>
       </c>
       <c r="I11" t="n">
-        <v>3432.096</v>
+        <v>1908.839484</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3432.096</v>
+        <v>1908.839484</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3070</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SWTCH</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.068951</v>
+      </c>
+      <c r="I12" t="n">
+        <v>211.67957</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>211.67957</v>
       </c>
     </row>
   </sheetData>
@@ -6556,66 +6948,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6641,16 +7033,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3923360528353861</v>
+        <v>0.3347222606834201</v>
       </c>
       <c r="I2" t="n">
-        <v>23.14782711728778</v>
+        <v>19.74861338032179</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>23.14782711728778</v>
+        <v>19.74861338032179</v>
       </c>
     </row>
     <row r="3">
@@ -6665,7 +7057,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>0.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6673,16 +7065,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0547832424675</v>
+        <v>154.3682946299502</v>
       </c>
       <c r="I3" t="n">
-        <v>210.1758789073169</v>
+        <v>15.43682946299502</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>210.1758789073169</v>
+        <v>15.43682946299502</v>
       </c>
     </row>
     <row r="4">
@@ -6710,16 +7102,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I4" t="n">
-        <v>58.99427315185414</v>
+        <v>58.97836357006049</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>58.99427315185414</v>
+        <v>58.97836357006049</v>
       </c>
     </row>
     <row r="5">
@@ -6734,24 +7126,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USDC</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.999601119255652</v>
       </c>
       <c r="I5" t="n">
-        <v>590.9426344533186</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>590.9426344533186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6774,16 +7166,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.664766241883815e-05</v>
+        <v>1.231132630434203e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>50.44241712907959</v>
+        <v>37.30331870215636</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>50.44241712907959</v>
+        <v>37.30331870215636</v>
       </c>
     </row>
     <row r="7">
@@ -6806,16 +7198,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.920754356690552</v>
+        <v>2.008710281543311</v>
       </c>
       <c r="I7" t="n">
-        <v>13.87358319428012</v>
+        <v>9.541373837330728</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13.87358319428012</v>
+        <v>9.541373837330728</v>
       </c>
     </row>
     <row r="8">
@@ -6830,7 +7222,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6838,48 +7230,48 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.920754356690552</v>
+        <v>2.008710281543311</v>
       </c>
       <c r="I8" t="n">
-        <v>2.920754356690552</v>
+        <v>56.24388788321271</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.920754356690552</v>
+        <v>56.24388788321271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>Spot</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>USDC</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.920754356690552</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I9" t="n">
-        <v>87.62263070071657</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>87.62263070071657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6894,7 +7286,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6902,16 +7294,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.000971254585602</v>
+        <v>0.999601119255652</v>
       </c>
       <c r="I10" t="n">
-        <v>500.4856272928012</v>
+        <v>199.9202238511304</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>500.4856272928012</v>
+        <v>199.9202238511304</v>
       </c>
     </row>
     <row r="11">
@@ -6926,7 +7318,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6934,16 +7326,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.000971254585602</v>
+        <v>0.999601119255652</v>
       </c>
       <c r="I11" t="n">
-        <v>365.3545079237449</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>365.3545079237449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6966,7 +7358,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>206.0547832424675</v>
+        <v>154.3682946299502</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6998,16 +7390,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.380795858267234</v>
+        <v>1.085733838059379</v>
       </c>
       <c r="I13" t="n">
-        <v>455.6626332281874</v>
+        <v>358.2921665595952</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>455.6626332281874</v>
+        <v>358.2921665595952</v>
       </c>
     </row>
     <row r="14">
@@ -7022,7 +7414,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -7030,16 +7422,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I14" t="n">
-        <v>3299.679684764723</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3299.679684764723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7054,7 +7446,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7062,16 +7454,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I15" t="n">
-        <v>113.9889345645995</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>113.9889345645995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -7086,7 +7478,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -7094,16 +7486,80 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I16" t="n">
-        <v>399.9611739108755</v>
+        <v>159.9413249357573</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>399.9611739108755</v>
+        <v>159.9413249357573</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kamino</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supplied</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>USDC</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9996332808484828</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1499.449921272724</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1499.449921272724</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kamino</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supplied</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>154.3682946299502</v>
+      </c>
+      <c r="I18" t="n">
+        <v>385.9207365748754</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>385.9207365748754</v>
       </c>
     </row>
   </sheetData>
@@ -7117,66 +7573,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7202,16 +7658,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3923360528353861</v>
+        <v>0.3347222606834201</v>
       </c>
       <c r="I2" t="n">
-        <v>35.15331033405059</v>
+        <v>29.99111455723444</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>35.15331033405059</v>
+        <v>29.99111455723444</v>
       </c>
     </row>
     <row r="3">
@@ -7226,7 +7682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.72</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7234,16 +7690,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0547832424675</v>
+        <v>154.3682946299502</v>
       </c>
       <c r="I3" t="n">
-        <v>354.4142271770442</v>
+        <v>108.0578062409651</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>354.4142271770442</v>
+        <v>108.0578062409651</v>
       </c>
     </row>
     <row r="4">
@@ -7258,7 +7714,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7266,16 +7722,48 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9999029347771888</v>
+        <v>0.9996332808484828</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5.428008715007262</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5.428008715007262</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kamino</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supplied</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>154.3682946299502</v>
+      </c>
+      <c r="I5" t="n">
+        <v>463.1048838898505</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>463.1048838898505</v>
       </c>
     </row>
   </sheetData>
@@ -7293,62 +7781,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7374,16 +7862,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3923360528353861</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I2" t="n">
-        <v>13.33942579640313</v>
+        <v>11.37281816946464</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>13.33942579640313</v>
+        <v>11.37281816946464</v>
       </c>
     </row>
     <row r="3">
@@ -7398,7 +7886,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.46</v>
+        <v>0.45</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7406,16 +7894,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0547832424675</v>
+        <v>154.2665544569048</v>
       </c>
       <c r="I3" t="n">
-        <v>300.8399835340026</v>
+        <v>69.41994950560716</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>300.8399835340026</v>
+        <v>69.41994950560716</v>
       </c>
     </row>
   </sheetData>
@@ -7433,62 +7921,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7514,16 +8002,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3925784961120431</v>
+        <v>0.3344946520430777</v>
       </c>
       <c r="I2" t="n">
-        <v>10.48184584619155</v>
+        <v>8.931007209550174</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10.48184584619155</v>
+        <v>8.931007209550174</v>
       </c>
     </row>
     <row r="3">
@@ -7546,16 +8034,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>206.0547832424675</v>
+        <v>154.2665544569048</v>
       </c>
       <c r="I3" t="n">
-        <v>119.0996647141462</v>
+        <v>89.16606847609097</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>119.0996647141462</v>
+        <v>89.16606847609097</v>
       </c>
     </row>
     <row r="4">
@@ -7578,16 +8066,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>115230.0028671602</v>
+        <v>102932.8306666245</v>
       </c>
       <c r="I4" t="n">
-        <v>169.9734726292907</v>
+        <v>151.8341598597245</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>169.9734726292907</v>
+        <v>151.8341598597245</v>
       </c>
     </row>
   </sheetData>

--- a/data/Web3 wallets.xlsx
+++ b/data/Web3 wallets.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" tabRatio="600" firstSheet="19" activeTab="30" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" tabRatio="600" firstSheet="21" activeTab="31" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="investment" sheetId="1" state="visible" r:id="rId1"/>
@@ -41,7 +41,9 @@
     <sheet name="monad main" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="monad NFTs" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="backpack mon" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="kraken" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="monad snipe" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="monad iphone" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="monad mevx" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -51,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,19 +89,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -123,27 +112,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -186,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,11 +174,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -738,66 +708,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -823,16 +793,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I2" t="n">
-        <v>588.0744424155663</v>
+        <v>616.6634411267964</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>588.0744424155663</v>
+        <v>616.6634411267964</v>
       </c>
     </row>
     <row r="3">
@@ -847,24 +817,88 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>294</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02698126595888046</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.932492191910855</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.932492191910855</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>118.12</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>EIGEN</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0.591693</v>
-      </c>
-      <c r="I3" t="n">
-        <v>69.89077716</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>69.89077716</v>
+      <c r="H4" t="n">
+        <v>0.478371</v>
+      </c>
+      <c r="I4" t="n">
+        <v>56.50518252</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>56.50518252</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2564</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHOG</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0039384</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.0980576</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.0980576</v>
       </c>
     </row>
   </sheetData>
@@ -882,62 +916,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -968,16 +1002,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I2" t="n">
-        <v>10.34301783142956</v>
+        <v>10.84583941680295</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10.34301783142956</v>
+        <v>10.84583941680295</v>
       </c>
     </row>
     <row r="3">
@@ -1005,16 +1039,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I3" t="n">
-        <v>2.955147951837017</v>
+        <v>3.0988112619437</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.955147951837017</v>
+        <v>3.0988112619437</v>
       </c>
     </row>
     <row r="4">
@@ -1042,16 +1076,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I4" t="n">
-        <v>11.82059180734807</v>
+        <v>12.3952450477748</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11.82059180734807</v>
+        <v>12.3952450477748</v>
       </c>
     </row>
     <row r="5">
@@ -1074,16 +1108,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I5" t="n">
-        <v>73.26993831784699</v>
+        <v>76.83192642863212</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>73.26993831784699</v>
+        <v>76.83192642863212</v>
       </c>
     </row>
     <row r="6">
@@ -1106,16 +1140,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I6" t="n">
-        <v>213.2328550865101</v>
+        <v>213.2268988653418</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>213.2328550865101</v>
+        <v>213.2268988653418</v>
       </c>
     </row>
     <row r="7">
@@ -1138,16 +1172,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.66949</v>
+        <v>0.6458</v>
       </c>
       <c r="I7" t="n">
-        <v>48.87277</v>
+        <v>47.1434</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>48.87277</v>
+        <v>47.1434</v>
       </c>
     </row>
   </sheetData>
@@ -1165,62 +1199,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1246,16 +1280,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>138.6917390381649</v>
+        <v>133.5957627334819</v>
       </c>
       <c r="I2" t="n">
-        <v>76.28045647099071</v>
+        <v>73.47766950341506</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>76.28045647099071</v>
+        <v>73.47766950341506</v>
       </c>
     </row>
     <row r="3">
@@ -1278,7 +1312,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1302,7 +1336,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1310,16 +1344,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
-        <v>612.8070331365714</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>612.8070331365714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1334,7 +1368,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1342,16 +1376,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>138.6917390381649</v>
+        <v>133.5957627334819</v>
       </c>
       <c r="I5" t="n">
-        <v>418.849051895258</v>
+        <v>404.7951610824501</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>418.849051895258</v>
+        <v>404.7951610824501</v>
       </c>
     </row>
   </sheetData>
@@ -1369,62 +1403,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1450,16 +1484,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.00026456673371</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I2" t="n">
-        <v>145.0383621763879</v>
+        <v>145.0216314765624</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>145.0383621763879</v>
+        <v>145.0216314765624</v>
       </c>
     </row>
     <row r="3">
@@ -1482,16 +1516,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>2.619984132837578</v>
+        <v>2.738121008401234</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.619984132837578</v>
+        <v>2.738121008401234</v>
       </c>
     </row>
     <row r="4">
@@ -1519,7 +1553,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1551,16 +1585,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>138.7351686529579</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I5" t="n">
-        <v>16.64822023835494</v>
+        <v>16.03292849716922</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16.64822023835494</v>
+        <v>16.03292849716922</v>
       </c>
     </row>
     <row r="6">
@@ -1583,16 +1617,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1649,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>88728.70538318102</v>
+        <v>90910.8221597407</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1647,16 +1681,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2484176440377943</v>
+        <v>0.2222285111734988</v>
       </c>
       <c r="I8" t="n">
-        <v>5.365821111216357</v>
+        <v>4.800135841347576</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5.365821111216357</v>
+        <v>4.800135841347576</v>
       </c>
     </row>
   </sheetData>
@@ -1674,62 +1708,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -1755,16 +1789,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
-        <v>116.0664258125897</v>
+        <v>115.9602450463181</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>116.0664258125897</v>
+        <v>115.9602450463181</v>
       </c>
     </row>
     <row r="3">
@@ -1787,16 +1821,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>3.791271156929672</v>
+        <v>3.962222165098256</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.791271156929672</v>
+        <v>3.962222165098256</v>
       </c>
     </row>
     <row r="4">
@@ -1824,7 +1858,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1856,16 +1890,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>138.7351686529579</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I5" t="n">
-        <v>22.19762698447326</v>
+        <v>21.37723799622562</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22.19762698447326</v>
+        <v>21.37723799622562</v>
       </c>
     </row>
     <row r="6">
@@ -1888,16 +1922,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
     </row>
     <row r="7">
@@ -1920,7 +1954,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.00026456673371</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1952,16 +1986,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2484176440377943</v>
+        <v>0.2222285111734988</v>
       </c>
       <c r="I8" t="n">
-        <v>5.390662875620135</v>
+        <v>4.822358692464925</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5.390662875620135</v>
+        <v>4.822358692464925</v>
       </c>
     </row>
   </sheetData>
@@ -1979,62 +2013,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2060,16 +2094,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.00026456673371</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I2" t="n">
-        <v>106.5781895854767</v>
+        <v>106.5658954057085</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>106.5781895854767</v>
+        <v>106.5658954057085</v>
       </c>
     </row>
     <row r="3">
@@ -2092,16 +2126,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.7351686529579</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I3" t="n">
-        <v>29.39798223756177</v>
+        <v>28.31147957125131</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>29.39798223756177</v>
+        <v>28.31147957125131</v>
       </c>
     </row>
     <row r="4">
@@ -2124,16 +2158,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.2484176440377943</v>
+        <v>0.2222285111734988</v>
       </c>
       <c r="I4" t="n">
-        <v>5.432893875106561</v>
+        <v>4.86013753936442</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5.432893875106561</v>
+        <v>4.86013753936442</v>
       </c>
     </row>
   </sheetData>
@@ -2151,62 +2185,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2232,16 +2266,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.00026456673371</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I2" t="n">
-        <v>112.9298695842358</v>
+        <v>112.9168427151993</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>112.9298695842358</v>
+        <v>112.9168427151993</v>
       </c>
     </row>
     <row r="3">
@@ -2264,16 +2298,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.7351686529579</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I3" t="n">
-        <v>12.81912958353331</v>
+        <v>12.3453549428203</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12.81912958353331</v>
+        <v>12.3453549428203</v>
       </c>
     </row>
     <row r="4">
@@ -2296,16 +2330,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.2484176440377943</v>
+        <v>0.2222285111734988</v>
       </c>
       <c r="I4" t="n">
-        <v>5.517355874079411</v>
+        <v>4.935695233163409</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5.517355874079411</v>
+        <v>4.935695233163409</v>
       </c>
     </row>
   </sheetData>
@@ -2323,62 +2357,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2409,7 +2443,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2441,7 +2475,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2473,16 +2507,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>23.30244711088481</v>
+        <v>24.35317038060391</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.30244711088481</v>
+        <v>24.35317038060391</v>
       </c>
     </row>
     <row r="5">
@@ -2505,7 +2539,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2537,7 +2571,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2564,62 +2598,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2650,7 +2684,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2682,16 +2716,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>10.78816995874297</v>
+        <v>11.27461591694626</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.78816995874297</v>
+        <v>11.27461591694626</v>
       </c>
     </row>
     <row r="4">
@@ -2714,16 +2748,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>38.52917842408203</v>
+        <v>40.2664854176652</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>38.52917842408203</v>
+        <v>40.2664854176652</v>
       </c>
     </row>
     <row r="5">
@@ -2746,7 +2780,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2773,62 +2807,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -2859,7 +2893,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2891,16 +2925,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>3.698801128711874</v>
+        <v>3.86558260009586</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.698801128711874</v>
+        <v>3.86558260009586</v>
       </c>
     </row>
     <row r="4">
@@ -2923,16 +2957,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>13.09992066418789</v>
+        <v>13.69060504200617</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13.09992066418789</v>
+        <v>13.69060504200617</v>
       </c>
     </row>
     <row r="5">
@@ -2955,7 +2989,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2995,62 +3029,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3081,7 +3115,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3113,16 +3147,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>2.774100846533906</v>
+        <v>2.899186950071895</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.774100846533906</v>
+        <v>2.899186950071895</v>
       </c>
     </row>
     <row r="4">
@@ -3145,16 +3179,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9317348382825</v>
+        <v>5.154110133461146</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9317348382825</v>
+        <v>5.154110133461146</v>
       </c>
     </row>
     <row r="5">
@@ -3177,7 +3211,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3204,62 +3238,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3290,7 +3324,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3322,16 +3356,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>2.619984132837578</v>
+        <v>2.738121008401234</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.619984132837578</v>
+        <v>2.738121008401234</v>
       </c>
     </row>
     <row r="4">
@@ -3354,16 +3388,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>9.47817789232418</v>
+        <v>9.90555541274564</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9.47817789232418</v>
+        <v>9.90555541274564</v>
       </c>
     </row>
     <row r="5">
@@ -3386,7 +3420,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>88728.70538318102</v>
+        <v>90910.8221597407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3413,62 +3447,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3499,7 +3533,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.000572636315428</v>
+        <v>0.9998114727217212</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3531,16 +3565,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I3" t="n">
-        <v>3.082334273926562</v>
+        <v>3.221318833413216</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.082334273926562</v>
+        <v>3.221318833413216</v>
       </c>
     </row>
     <row r="4">
@@ -3563,16 +3597,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I4" t="n">
-        <v>7.829129055773469</v>
+        <v>8.18214983686957</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7.829129055773469</v>
+        <v>8.18214983686957</v>
       </c>
     </row>
     <row r="5">
@@ -3595,7 +3629,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.541167136963281</v>
+        <v>1.610659416706608</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3622,62 +3656,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3708,7 +3742,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3740,16 +3774,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>3.087174486295518</v>
+        <v>3.216857301521635</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.087174486295518</v>
+        <v>3.216857301521635</v>
       </c>
     </row>
     <row r="4">
@@ -3772,16 +3806,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>19.85053194688018</v>
+        <v>20.68439244878411</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19.85053194688018</v>
+        <v>20.68439244878411</v>
       </c>
     </row>
     <row r="5">
@@ -3804,7 +3838,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9995794870364022</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3831,62 +3865,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -3917,7 +3951,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3949,16 +3983,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>4.630761729443277</v>
+        <v>4.825285952282453</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.630761729443277</v>
+        <v>4.825285952282453</v>
       </c>
     </row>
     <row r="4">
@@ -3981,16 +4015,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>32.41533210610294</v>
+        <v>33.77700166597717</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>32.41533210610294</v>
+        <v>33.77700166597717</v>
       </c>
     </row>
     <row r="5">
@@ -4013,7 +4047,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4040,62 +4074,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4126,7 +4160,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4158,16 +4192,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>5.402555351017157</v>
+        <v>5.629500277662862</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5.402555351017157</v>
+        <v>5.629500277662862</v>
       </c>
     </row>
     <row r="4">
@@ -4190,16 +4224,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>34.39112377733208</v>
+        <v>35.83579033895102</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>34.39112377733208</v>
+        <v>35.83579033895102</v>
       </c>
     </row>
     <row r="5">
@@ -4222,7 +4256,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4254,7 +4288,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9995794870364022</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4281,62 +4315,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4367,7 +4401,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4399,16 +4433,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>6.483066421220588</v>
+        <v>6.755400333195435</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6.483066421220588</v>
+        <v>6.755400333195435</v>
       </c>
     </row>
     <row r="4">
@@ -4431,16 +4465,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>29.32815761980742</v>
+        <v>30.56014436445554</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>29.32815761980742</v>
+        <v>30.56014436445554</v>
       </c>
     </row>
     <row r="5">
@@ -4463,7 +4497,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4490,62 +4524,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4576,7 +4610,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4608,16 +4642,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>1.852304691777311</v>
+        <v>1.930114380912981</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.852304691777311</v>
+        <v>1.930114380912981</v>
       </c>
     </row>
     <row r="4">
@@ -4640,16 +4674,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>1.852304691777311</v>
+        <v>1.930114380912981</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.852304691777311</v>
+        <v>1.930114380912981</v>
       </c>
     </row>
     <row r="5">
@@ -4672,7 +4706,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4699,62 +4733,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4785,7 +4819,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4817,16 +4851,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I3" t="n">
-        <v>4.93947917807283</v>
+        <v>5.146971682434617</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.93947917807283</v>
+        <v>5.146971682434617</v>
       </c>
     </row>
     <row r="4">
@@ -4849,16 +4883,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.543587243147759</v>
+        <v>1.608428650760818</v>
       </c>
       <c r="I4" t="n">
-        <v>4.260300791087815</v>
+        <v>4.439263076099857</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4.260300791087815</v>
+        <v>4.439263076099857</v>
       </c>
     </row>
     <row r="5">
@@ -4881,7 +4915,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9995678551414029</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4908,62 +4942,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -4981,7 +5015,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>154.65</v>
+        <v>6089.71</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4989,16 +5023,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.999673763980827</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I2" t="n">
-        <v>154.5995475996349</v>
+        <v>6090.61847875267</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>154.5995475996349</v>
+        <v>6090.61847875267</v>
       </c>
     </row>
     <row r="3">
@@ -5013,7 +5047,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1887</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5021,16 +5055,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.08307441833284641</v>
+        <v>0.07166302813236344</v>
       </c>
       <c r="I3" t="n">
-        <v>156.7614273940812</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>156.7614273940812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5053,16 +5087,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.362115667686528</v>
+        <v>5.691257117471511</v>
       </c>
       <c r="I4" t="n">
-        <v>435.8049232365272</v>
+        <v>389.8511125467985</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>435.8049232365272</v>
+        <v>389.8511125467985</v>
       </c>
     </row>
     <row r="5">
@@ -5085,16 +5119,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.2620584190731858</v>
+        <v>0.2716638027840671</v>
       </c>
       <c r="I5" t="n">
-        <v>379.9847076561194</v>
+        <v>393.9125140368973</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>379.9847076561194</v>
+        <v>393.9125140368973</v>
       </c>
     </row>
     <row r="6">
@@ -5109,7 +5143,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>531.4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5117,16 +5151,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.2499104540200931</v>
+        <v>0.2162935777789983</v>
       </c>
       <c r="I6" t="n">
-        <v>132.8024152662775</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>132.8024152662775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5141,7 +5175,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>235.8</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5149,16 +5183,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.307903563262203</v>
+        <v>0.2703748961130239</v>
       </c>
       <c r="I7" t="n">
-        <v>72.60366021722747</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>72.60366021722747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5173,7 +5207,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>864365</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5181,16 +5215,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.0004835964149946033</v>
+        <v>0.0004530679316510341</v>
       </c>
       <c r="I8" t="n">
-        <v>418.0038152468103</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>418.0038152468103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5213,16 +5247,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>294.7223784294339</v>
+        <v>282.8866108549931</v>
       </c>
       <c r="I9" t="n">
-        <v>382.7559528663058</v>
+        <v>367.3848415173796</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>382.7559528663058</v>
+        <v>367.3848415173796</v>
       </c>
     </row>
     <row r="10">
@@ -5237,7 +5271,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5245,16 +5279,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.205963300744764</v>
+        <v>3.451792946946258</v>
       </c>
       <c r="I10" t="n">
-        <v>92.11059628631033</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>92.11059628631033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5269,7 +5303,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1040.6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5277,16 +5311,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1427579896588138</v>
+        <v>0.1116370996630137</v>
       </c>
       <c r="I11" t="n">
-        <v>148.5539640389617</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>148.5539640389617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5301,7 +5335,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400010</v>
+        <v>220010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5309,16 +5343,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I12" t="n">
-        <v>13316.31675783985</v>
+        <v>5924.143288571171</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13316.31675783985</v>
+        <v>5924.143288571171</v>
       </c>
     </row>
     <row r="13">
@@ -5341,7 +5375,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.04288708</v>
+        <v>0.04094215</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -5917,62 +5951,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -5990,7 +6024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>517</v>
+        <v>763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5998,16 +6032,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.999673763980827</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I2" t="n">
-        <v>516.8313359780875</v>
+        <v>763.1138263214975</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>516.8313359780875</v>
+        <v>763.1138263214975</v>
       </c>
     </row>
     <row r="3">
@@ -6030,16 +6064,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.240242598592219</v>
+        <v>2.069594550301658</v>
       </c>
       <c r="I3" t="n">
-        <v>147.8560115070864</v>
+        <v>136.5932403199095</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>147.8560115070864</v>
+        <v>136.5932403199095</v>
       </c>
     </row>
     <row r="4">
@@ -6062,7 +6096,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.2620584190731858</v>
+        <v>0.2716638027840671</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -6086,7 +6120,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>672.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6094,16 +6128,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.999673763980827</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I5" t="n">
-        <v>43.98564561515639</v>
+        <v>672.80035513299</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>43.98564561515639</v>
+        <v>672.80035513299</v>
       </c>
     </row>
     <row r="6">
@@ -6126,16 +6160,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.02142021</v>
+        <v>0.01189772</v>
       </c>
       <c r="I6" t="n">
-        <v>50.1232914</v>
+        <v>27.8406648</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>50.1232914</v>
+        <v>27.8406648</v>
       </c>
     </row>
   </sheetData>
@@ -6153,62 +6187,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6234,16 +6268,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>138.9070833329881</v>
+        <v>133.3706134973307</v>
       </c>
       <c r="I2" t="n">
-        <v>2.250294749994407</v>
+        <v>2.160603938656756</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.250294749994407</v>
+        <v>2.160603938656756</v>
       </c>
     </row>
     <row r="3">
@@ -6266,16 +6300,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.01113934</v>
+        <v>0.00897601</v>
       </c>
       <c r="I3" t="n">
-        <v>133.67208</v>
+        <v>107.71212</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>133.67208</v>
+        <v>107.71212</v>
       </c>
     </row>
   </sheetData>
@@ -6289,66 +6323,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6374,16 +6408,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>138.9070833329881</v>
+        <v>133.3706134973307</v>
       </c>
       <c r="I2" t="n">
-        <v>50.00654999987572</v>
+        <v>48.01342085903903</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>50.00654999987572</v>
+        <v>48.01342085903903</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6432,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1100000</v>
+        <v>250000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6406,16 +6440,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I3" t="n">
-        <v>36618.95561016933</v>
+        <v>6731.67502451158</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>36618.95561016933</v>
+        <v>6731.67502451158</v>
       </c>
     </row>
     <row r="4">
@@ -6438,7 +6472,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.999673763980827</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -6470,16 +6504,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9997172129749611</v>
+        <v>0.999887343274052</v>
       </c>
       <c r="I5" t="n">
-        <v>2569.27323734565</v>
+        <v>2569.710472214314</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2569.27323734565</v>
+        <v>2569.710472214314</v>
       </c>
     </row>
     <row r="6">
@@ -6502,16 +6536,112 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>138.9070833329881</v>
+        <v>133.3706134973307</v>
       </c>
       <c r="I6" t="n">
-        <v>277.8141666659762</v>
+        <v>266.7412269946613</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>277.8141666659762</v>
+        <v>266.7412269946613</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gmonads</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Staked</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>700000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02692670009804632</v>
+      </c>
+      <c r="I7" t="n">
+        <v>18848.69006863242</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18848.69006863242</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fastlane</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Staked</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02692670009804632</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10770.68003921853</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10770.68003921853</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kintsu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Staked</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02692670009804632</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5385.340019609263</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5385.340019609263</v>
       </c>
     </row>
   </sheetData>
@@ -6525,66 +6655,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6602,7 +6732,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6610,16 +6740,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I2" t="n">
-        <v>3328.995964560848</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3328.995964560848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6634,7 +6764,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6642,16 +6772,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I3" t="n">
-        <v>3328.995964560848</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3328.995964560848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6666,7 +6796,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15468.4</v>
+        <v>83907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6674,16 +6804,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I4" t="n">
-        <v>514.9424117821303</v>
+        <v>2259.338625126773</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>514.9424117821303</v>
+        <v>2259.338625126773</v>
       </c>
     </row>
     <row r="5">
@@ -6698,7 +6828,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>522.5599999999999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6706,16 +6836,80 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9997172129749611</v>
+        <v>0.999887343274052</v>
       </c>
       <c r="I5" t="n">
-        <v>89.9745491677465</v>
+        <v>522.5011301012886</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>89.9745491677465</v>
+        <v>522.5011301012886</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>90904.28192033779</v>
+      </c>
+      <c r="I6" t="n">
+        <v>390.8884122574525</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>390.8884122574525</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09418</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3098.64632654872</v>
+      </c>
+      <c r="I7" t="n">
+        <v>291.8305110343584</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>291.8305110343584</v>
       </c>
     </row>
   </sheetData>
@@ -6733,62 +6927,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6806,7 +7000,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>147460</v>
+        <v>9433.809999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6814,16 +7008,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I2" t="n">
-        <v>4908.937449341427</v>
+        <v>254.0213726519503</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4908.937449341427</v>
+        <v>254.0213726519503</v>
       </c>
     </row>
   </sheetData>
@@ -6841,62 +7035,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -6914,7 +7108,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>32930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6922,16 +7116,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9986987893682545</v>
+        <v>886.6962342286653</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9986987893682545</v>
+        <v>886.6962342286653</v>
       </c>
     </row>
     <row r="3">
@@ -6946,7 +7140,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6954,16 +7148,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02692670009804632</v>
       </c>
       <c r="I3" t="n">
-        <v>6657.991929121697</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6657.991929121697</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6981,62 +7175,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7054,7 +7248,223 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500051</v>
+        <v>120000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.02692670009804632</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3231.204011765558</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3231.204011765558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>rewards ticker</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>prices</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>rewards prices</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>rewards value</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>total value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.02693614155414653</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3501.69840203905</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3501.69840203905</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>rewards ticker</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>prices</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>rewards prices</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>rewards value</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>total value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7065,17 +7475,53 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.03328995964560848</v>
+        <v>0.02693614155414653</v>
       </c>
       <c r="I2" t="n">
-        <v>16646.67761074617</v>
+        <v>224.9167819771235</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16646.67761074617</v>
+        <v>224.9167819771235</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>649100</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHOG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0.00388284</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2520.351444</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2520.351444</v>
       </c>
     </row>
   </sheetData>
@@ -7214,62 +7660,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7295,16 +7741,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2483912578854215</v>
+        <v>0.2222466660012797</v>
       </c>
       <c r="I2" t="n">
-        <v>36.76190616704238</v>
+        <v>32.8925065681894</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>36.76190616704238</v>
+        <v>32.8925065681894</v>
       </c>
     </row>
     <row r="3">
@@ -7319,24 +7765,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>302.59</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USDC</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9996852090319271</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>302.6351411620209</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>302.6351411620209</v>
       </c>
     </row>
     <row r="4">
@@ -7364,7 +7810,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -7388,7 +7834,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1862</v>
+        <v>1.92</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -7396,16 +7842,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I5" t="n">
-        <v>25.82440180890631</v>
+        <v>256.5268559547075</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>25.82440180890631</v>
+        <v>256.5268559547075</v>
       </c>
     </row>
     <row r="6">
@@ -7420,7 +7866,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.08089</v>
+        <v>0.04045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7428,16 +7874,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2955.147951837017</v>
+        <v>3098.811261943701</v>
       </c>
       <c r="I6" t="n">
-        <v>239.0419178240963</v>
+        <v>125.3469155456227</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>239.0419178240963</v>
+        <v>125.3469155456227</v>
       </c>
     </row>
     <row r="7">
@@ -7452,7 +7898,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.00662</v>
+        <v>0.00331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7460,16 +7906,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>88605.29982659531</v>
+        <v>90890.54705683842</v>
       </c>
       <c r="I7" t="n">
-        <v>586.5670848520609</v>
+        <v>300.8477107581352</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>586.5670848520609</v>
+        <v>300.8477107581352</v>
       </c>
     </row>
     <row r="8">
@@ -7492,16 +7938,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.539355115248893</v>
+        <v>1.610966937878629</v>
       </c>
       <c r="I8" t="n">
-        <v>10.77548580674225</v>
+        <v>11.27676856515041</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10.77548580674225</v>
+        <v>11.27676856515041</v>
       </c>
     </row>
     <row r="9">
@@ -7524,16 +7970,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.539355115248893</v>
+        <v>1.610966937878629</v>
       </c>
       <c r="I9" t="n">
-        <v>42.17833015781966</v>
+        <v>44.14049409787444</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>42.17833015781966</v>
+        <v>44.14049409787444</v>
       </c>
     </row>
     <row r="10">
@@ -7556,7 +8002,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.539355115248893</v>
+        <v>1.610966937878629</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -7580,7 +8026,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27684</v>
+        <v>23085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -7588,16 +8034,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.04289055</v>
+        <v>0.04089743</v>
       </c>
       <c r="I11" t="n">
-        <v>1187.3819862</v>
+        <v>944.11717155</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1187.3819862</v>
+        <v>944.11717155</v>
       </c>
     </row>
     <row r="12">
@@ -7612,7 +8058,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3070</v>
+        <v>6910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7620,16 +8066,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.04289055</v>
+        <v>0.04089743</v>
       </c>
       <c r="I12" t="n">
-        <v>131.6739885</v>
+        <v>282.6012413</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>131.6739885</v>
+        <v>282.6012413</v>
       </c>
     </row>
   </sheetData>
@@ -7647,62 +8093,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -7728,16 +8174,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2483912578854215</v>
+        <v>0.2222466660012797</v>
       </c>
       <c r="I2" t="n">
-        <v>14.65508421523987</v>
+        <v>13.1125532940755</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>14.65508421523987</v>
+        <v>13.1125532940755</v>
       </c>
     </row>
     <row r="3">
@@ -7752,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7760,16 +8206,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I3" t="n">
-        <v>13.86917390381649</v>
+        <v>40.08232124292304</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13.86917390381649</v>
+        <v>40.08232124292304</v>
       </c>
     </row>
     <row r="4">
@@ -7797,7 +8243,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -7829,7 +8275,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.999619524020517</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7861,16 +8307,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9.999791652545198e-06</v>
+        <v>9.217411151568946e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>30.29936870721195</v>
+        <v>27.92875578925391</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>30.29936870721195</v>
+        <v>27.92875578925391</v>
       </c>
     </row>
     <row r="7">
@@ -7893,16 +8339,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.539355115248893</v>
+        <v>1.610966937878629</v>
       </c>
       <c r="I7" t="n">
-        <v>7.31193679743224</v>
+        <v>7.652092954923489</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7.31193679743224</v>
+        <v>7.652092954923489</v>
       </c>
     </row>
     <row r="8">
@@ -7925,16 +8371,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.539355115248893</v>
+        <v>1.610966937878629</v>
       </c>
       <c r="I8" t="n">
-        <v>43.101943226969</v>
+        <v>45.10707426060162</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>43.101943226969</v>
+        <v>45.10707426060162</v>
       </c>
     </row>
     <row r="9">
@@ -7957,7 +8403,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7989,16 +8435,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.999619524020517</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I10" t="n">
-        <v>199.9239048041034</v>
+        <v>200.0298365193965</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>199.9239048041034</v>
+        <v>200.0298365193965</v>
       </c>
     </row>
     <row r="11">
@@ -8021,7 +8467,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.999619524020517</v>
+        <v>1.000149182596982</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -8053,7 +8499,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -8085,16 +8531,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.159014856720684</v>
+        <v>0.9401065456253799</v>
       </c>
       <c r="I13" t="n">
-        <v>382.4749027178258</v>
+        <v>310.2351600563754</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>382.4749027178258</v>
+        <v>310.2351600563754</v>
       </c>
     </row>
     <row r="14">
@@ -8117,7 +8563,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -8149,7 +8595,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8181,16 +8627,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I16" t="n">
-        <v>159.9496334451083</v>
+        <v>159.9451655811284</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>159.9496334451083</v>
+        <v>159.9451655811284</v>
       </c>
     </row>
     <row r="17">
@@ -8213,7 +8659,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -8245,7 +8691,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -8272,62 +8718,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -8353,16 +8799,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2483912578854215</v>
+        <v>0.2222466660012797</v>
       </c>
       <c r="I2" t="n">
-        <v>22.25585670653377</v>
+        <v>19.91330127371466</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>22.25585670653377</v>
+        <v>19.91330127371466</v>
       </c>
     </row>
     <row r="3">
@@ -8377,7 +8823,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -8385,16 +8831,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I3" t="n">
-        <v>97.08421732671543</v>
+        <v>46.76270811674355</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>97.08421732671543</v>
+        <v>46.76270811674355</v>
       </c>
     </row>
     <row r="4">
@@ -8409,7 +8855,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.43</v>
+        <v>54.46</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -8417,16 +8863,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9996852090319271</v>
+        <v>0.9996572848820523</v>
       </c>
       <c r="I4" t="n">
-        <v>5.428290685043364</v>
+        <v>54.44133573467657</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5.428290685043364</v>
+        <v>54.44133573467657</v>
       </c>
     </row>
     <row r="5">
@@ -8449,16 +8895,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I5" t="n">
-        <v>416.0752171144948</v>
+        <v>400.8232124292304</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>416.0752171144948</v>
+        <v>400.8232124292304</v>
       </c>
     </row>
   </sheetData>
@@ -8476,62 +8922,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -8557,16 +9003,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2483912578854215</v>
+        <v>0.2222466660012797</v>
       </c>
       <c r="I2" t="n">
-        <v>8.445302768104332</v>
+        <v>7.55638664404351</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>8.445302768104332</v>
+        <v>7.55638664404351</v>
       </c>
     </row>
     <row r="3">
@@ -8589,16 +9035,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.6917390381649</v>
+        <v>133.6077374764101</v>
       </c>
       <c r="I3" t="n">
-        <v>62.41128256717421</v>
+        <v>60.12348186438457</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>62.41128256717421</v>
+        <v>60.12348186438457</v>
       </c>
     </row>
   </sheetData>
@@ -8616,62 +9062,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>app</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>rewards ticker</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>prices</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>rewards prices</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>rewards value</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>total value</t>
         </is>
@@ -8697,16 +9143,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2484176440377943</v>
+        <v>0.2222326703341569</v>
       </c>
       <c r="I2" t="n">
-        <v>6.632751095809106</v>
+        <v>5.933612297921989</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6.632751095809106</v>
+        <v>5.933612297921989</v>
       </c>
     </row>
     <row r="3">
@@ -8729,16 +9175,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>138.6917390381649</v>
+        <v>133.5957627334819</v>
       </c>
       <c r="I3" t="n">
-        <v>80.16382516405932</v>
+        <v>77.21835085995254</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>80.16382516405932</v>
+        <v>77.21835085995254</v>
       </c>
     </row>
     <row r="4">
@@ -8761,16 +9207,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>88605.29982659531</v>
+        <v>90906.86355319993</v>
       </c>
       <c r="I4" t="n">
-        <v>130.6999056682142</v>
+        <v>134.0948962900542</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>130.6999056682142</v>
+        <v>134.0948962900542</v>
       </c>
     </row>
   </sheetData>
